--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D608B01-63AE-4F20-B60C-9546D8731AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BF09D0-31F2-4FD5-8456-372F33253326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5210,7 +5210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C671A2-0046-4B1B-94B6-8B39D6287276}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AB215C-D3D8-4468-AF84-6CA9997BC88C}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040E277B-B3FB-4F52-A209-F707A85E75B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53641234-BD52-4142-BFD1-634558A53A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9D60C7-6686-452A-B5A7-C888AC4534A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09061844-2F79-4A7E-93F6-8F608D885F5C}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53641234-BD52-4142-BFD1-634558A53A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E6DA23-6742-44BA-9D75-0D47A71DE323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09061844-2F79-4A7E-93F6-8F608D885F5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4C74E5-EEDA-4581-B60B-F700C0195564}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E6DA23-6742-44BA-9D75-0D47A71DE323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1C5DC8-1625-4FDB-AABE-D631C158D512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4C74E5-EEDA-4581-B60B-F700C0195564}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF165C-90E1-4BDC-B49E-36665D1EE20F}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1C5DC8-1625-4FDB-AABE-D631C158D512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579EF4D5-613F-4463-BB7D-3E03E91EA8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF165C-90E1-4BDC-B49E-36665D1EE20F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F423732-D450-4381-86D2-D57E24EED99C}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579EF4D5-613F-4463-BB7D-3E03E91EA8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201A5402-47B2-4732-980B-A147083841B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F423732-D450-4381-86D2-D57E24EED99C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47ADB978-A1A4-4115-B6D0-FFAA1E658903}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201A5402-47B2-4732-980B-A147083841B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C674994-900E-4A17-AAF4-40D928B468C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47ADB978-A1A4-4115-B6D0-FFAA1E658903}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C33A4E-4384-4B86-B785-95F1D10DB213}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C674994-900E-4A17-AAF4-40D928B468C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED9C4E5-D3A9-4C48-9251-E5DAE56507D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C33A4E-4384-4B86-B785-95F1D10DB213}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632E9762-65AA-4706-B9AF-82F4A9215948}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED9C4E5-D3A9-4C48-9251-E5DAE56507D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D726652-0EBE-4697-A9AB-BCBF69299257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632E9762-65AA-4706-B9AF-82F4A9215948}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313F2E5A-8D03-4011-86ED-19DB253B3578}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D726652-0EBE-4697-A9AB-BCBF69299257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FACB90-43EE-4C28-97D5-0B62AA70ABBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7778,7 +7778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313F2E5A-8D03-4011-86ED-19DB253B3578}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B8B777E-3AC6-4E77-820F-D38268D35F7A}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2FDD82-AB25-4FBB-B81D-E33BAC1601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3983AE-83AD-419C-AABD-C246030E160B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4244,7 +4244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D9B66C-EE51-4CED-AD1C-F7907CB0FB71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D58A7E-F695-45D1-B485-12233CFE07F4}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3983AE-83AD-419C-AABD-C246030E160B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC7151A-5E54-469C-8EBC-F1A2E948B3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4244,7 +4244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D58A7E-F695-45D1-B485-12233CFE07F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039440E5-AA72-4DA8-B54A-C223ACE20607}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC7151A-5E54-469C-8EBC-F1A2E948B3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDC69B1-CF2A-40E1-8DC7-699CE945D26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4244,7 +4244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039440E5-AA72-4DA8-B54A-C223ACE20607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9874B7-04B6-41BF-961B-D0A6B85308A7}">
   <dimension ref="B3:H130"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SysSettings.xlsx
+++ b/VerveStacks_NZL_grids/SysSettings.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDC69B1-CF2A-40E1-8DC7-699CE945D26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6FCB61-B6CE-431E-AD88-3B41FECD6EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
-    <sheet name="grids" sheetId="7" r:id="rId2"/>
-    <sheet name="fuels" sheetId="2" r:id="rId3"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId4"/>
+    <sheet name="fuels" sheetId="2" r:id="rId2"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId3"/>
+    <sheet name="grids" sheetId="7" r:id="rId4"/>
     <sheet name="System Settings" sheetId="4" r:id="rId5"/>
     <sheet name="Constants" sheetId="5" r:id="rId6"/>
     <sheet name="reporting options" sheetId="6" r:id="rId7"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="598">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -675,6 +675,9 @@
   </si>
   <si>
     <t>OIL</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
   </si>
   <si>
     <t>NZL</t>
@@ -4220,7 +4223,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -4244,2942 +4247,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9874B7-04B6-41BF-961B-D0A6B85308A7}">
-  <dimension ref="B3:H130"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="3" spans="2:8">
-      <c r="B3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>346</v>
-      </c>
-      <c r="H6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s">
-        <v>346</v>
-      </c>
-      <c r="H7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>346</v>
-      </c>
-      <c r="H8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>353</v>
-      </c>
-      <c r="D9" t="s">
-        <v>354</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>355</v>
-      </c>
-      <c r="D10" t="s">
-        <v>356</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>346</v>
-      </c>
-      <c r="H10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>357</v>
-      </c>
-      <c r="D11" t="s">
-        <v>358</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>346</v>
-      </c>
-      <c r="H11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" t="s">
-        <v>346</v>
-      </c>
-      <c r="H12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>361</v>
-      </c>
-      <c r="D13" t="s">
-        <v>362</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>346</v>
-      </c>
-      <c r="H13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D14" t="s">
-        <v>364</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>346</v>
-      </c>
-      <c r="H14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>365</v>
-      </c>
-      <c r="D15" t="s">
-        <v>366</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" t="s">
-        <v>346</v>
-      </c>
-      <c r="H15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>367</v>
-      </c>
-      <c r="D16" t="s">
-        <v>368</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>346</v>
-      </c>
-      <c r="H16" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>369</v>
-      </c>
-      <c r="D17" t="s">
-        <v>370</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" t="s">
-        <v>346</v>
-      </c>
-      <c r="H17" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>371</v>
-      </c>
-      <c r="D18" t="s">
-        <v>372</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>346</v>
-      </c>
-      <c r="H18" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" t="s">
-        <v>374</v>
-      </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" t="s">
-        <v>346</v>
-      </c>
-      <c r="H19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>375</v>
-      </c>
-      <c r="D20" t="s">
-        <v>376</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" t="s">
-        <v>346</v>
-      </c>
-      <c r="H20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>377</v>
-      </c>
-      <c r="D21" t="s">
-        <v>378</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>346</v>
-      </c>
-      <c r="H21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>379</v>
-      </c>
-      <c r="D22" t="s">
-        <v>380</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" t="s">
-        <v>346</v>
-      </c>
-      <c r="H22" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>381</v>
-      </c>
-      <c r="D23" t="s">
-        <v>382</v>
-      </c>
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" t="s">
-        <v>346</v>
-      </c>
-      <c r="H23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>383</v>
-      </c>
-      <c r="D24" t="s">
-        <v>384</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" t="s">
-        <v>346</v>
-      </c>
-      <c r="H24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>385</v>
-      </c>
-      <c r="D25" t="s">
-        <v>386</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" t="s">
-        <v>346</v>
-      </c>
-      <c r="H25" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" t="s">
-        <v>387</v>
-      </c>
-      <c r="D26" t="s">
-        <v>388</v>
-      </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" t="s">
-        <v>346</v>
-      </c>
-      <c r="H26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>389</v>
-      </c>
-      <c r="D27" t="s">
-        <v>390</v>
-      </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" t="s">
-        <v>346</v>
-      </c>
-      <c r="H27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>391</v>
-      </c>
-      <c r="D28" t="s">
-        <v>392</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" t="s">
-        <v>346</v>
-      </c>
-      <c r="H28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" t="s">
-        <v>393</v>
-      </c>
-      <c r="D29" t="s">
-        <v>394</v>
-      </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" t="s">
-        <v>346</v>
-      </c>
-      <c r="H29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>395</v>
-      </c>
-      <c r="D30" t="s">
-        <v>396</v>
-      </c>
-      <c r="E30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" t="s">
-        <v>346</v>
-      </c>
-      <c r="H30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>397</v>
-      </c>
-      <c r="D31" t="s">
-        <v>398</v>
-      </c>
-      <c r="E31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" t="s">
-        <v>346</v>
-      </c>
-      <c r="H31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" t="s">
-        <v>399</v>
-      </c>
-      <c r="D32" t="s">
-        <v>400</v>
-      </c>
-      <c r="E32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" t="s">
-        <v>346</v>
-      </c>
-      <c r="H32" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>401</v>
-      </c>
-      <c r="D33" t="s">
-        <v>402</v>
-      </c>
-      <c r="E33" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" t="s">
-        <v>346</v>
-      </c>
-      <c r="H33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>403</v>
-      </c>
-      <c r="D34" t="s">
-        <v>404</v>
-      </c>
-      <c r="E34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" t="s">
-        <v>346</v>
-      </c>
-      <c r="H34" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>405</v>
-      </c>
-      <c r="D35" t="s">
-        <v>406</v>
-      </c>
-      <c r="E35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" t="s">
-        <v>346</v>
-      </c>
-      <c r="H35" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" t="s">
-        <v>407</v>
-      </c>
-      <c r="D36" t="s">
-        <v>408</v>
-      </c>
-      <c r="E36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" t="s">
-        <v>346</v>
-      </c>
-      <c r="H36" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" t="s">
-        <v>409</v>
-      </c>
-      <c r="D37" t="s">
-        <v>410</v>
-      </c>
-      <c r="E37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" t="s">
-        <v>346</v>
-      </c>
-      <c r="H37" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" t="s">
-        <v>411</v>
-      </c>
-      <c r="D38" t="s">
-        <v>412</v>
-      </c>
-      <c r="E38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G38" t="s">
-        <v>346</v>
-      </c>
-      <c r="H38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" t="s">
-        <v>413</v>
-      </c>
-      <c r="D39" t="s">
-        <v>414</v>
-      </c>
-      <c r="E39" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" t="s">
-        <v>346</v>
-      </c>
-      <c r="H39" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" t="s">
-        <v>415</v>
-      </c>
-      <c r="D40" t="s">
-        <v>416</v>
-      </c>
-      <c r="E40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" t="s">
-        <v>346</v>
-      </c>
-      <c r="H40" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" t="s">
-        <v>417</v>
-      </c>
-      <c r="D41" t="s">
-        <v>418</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" t="s">
-        <v>346</v>
-      </c>
-      <c r="H41" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" t="s">
-        <v>419</v>
-      </c>
-      <c r="D42" t="s">
-        <v>420</v>
-      </c>
-      <c r="E42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" t="s">
-        <v>346</v>
-      </c>
-      <c r="H42" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" t="s">
-        <v>421</v>
-      </c>
-      <c r="D43" t="s">
-        <v>422</v>
-      </c>
-      <c r="E43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" t="s">
-        <v>346</v>
-      </c>
-      <c r="H43" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="s">
-        <v>423</v>
-      </c>
-      <c r="D44" t="s">
-        <v>424</v>
-      </c>
-      <c r="E44" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" t="s">
-        <v>346</v>
-      </c>
-      <c r="H44" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" t="s">
-        <v>425</v>
-      </c>
-      <c r="D45" t="s">
-        <v>426</v>
-      </c>
-      <c r="E45" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" t="s">
-        <v>346</v>
-      </c>
-      <c r="H45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" t="s">
-        <v>427</v>
-      </c>
-      <c r="D46" t="s">
-        <v>428</v>
-      </c>
-      <c r="E46" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" t="s">
-        <v>346</v>
-      </c>
-      <c r="H46" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>429</v>
-      </c>
-      <c r="D47" t="s">
-        <v>430</v>
-      </c>
-      <c r="E47" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" t="s">
-        <v>346</v>
-      </c>
-      <c r="H47" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" t="s">
-        <v>431</v>
-      </c>
-      <c r="D48" t="s">
-        <v>432</v>
-      </c>
-      <c r="E48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" t="s">
-        <v>346</v>
-      </c>
-      <c r="H48" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>433</v>
-      </c>
-      <c r="D49" t="s">
-        <v>434</v>
-      </c>
-      <c r="E49" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" t="s">
-        <v>35</v>
-      </c>
-      <c r="G49" t="s">
-        <v>346</v>
-      </c>
-      <c r="H49" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" t="s">
-        <v>435</v>
-      </c>
-      <c r="D50" t="s">
-        <v>436</v>
-      </c>
-      <c r="E50" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" t="s">
-        <v>346</v>
-      </c>
-      <c r="H50" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" t="s">
-        <v>437</v>
-      </c>
-      <c r="D51" t="s">
-        <v>438</v>
-      </c>
-      <c r="E51" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" t="s">
-        <v>346</v>
-      </c>
-      <c r="H51" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" t="s">
-        <v>439</v>
-      </c>
-      <c r="D52" t="s">
-        <v>440</v>
-      </c>
-      <c r="E52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" t="s">
-        <v>346</v>
-      </c>
-      <c r="H52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>441</v>
-      </c>
-      <c r="D53" t="s">
-        <v>442</v>
-      </c>
-      <c r="E53" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" t="s">
-        <v>346</v>
-      </c>
-      <c r="H53" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>443</v>
-      </c>
-      <c r="D54" t="s">
-        <v>444</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" t="s">
-        <v>35</v>
-      </c>
-      <c r="G54" t="s">
-        <v>346</v>
-      </c>
-      <c r="H54" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>445</v>
-      </c>
-      <c r="D55" t="s">
-        <v>446</v>
-      </c>
-      <c r="E55" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" t="s">
-        <v>35</v>
-      </c>
-      <c r="G55" t="s">
-        <v>346</v>
-      </c>
-      <c r="H55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>447</v>
-      </c>
-      <c r="D56" t="s">
-        <v>448</v>
-      </c>
-      <c r="E56" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" t="s">
-        <v>35</v>
-      </c>
-      <c r="G56" t="s">
-        <v>346</v>
-      </c>
-      <c r="H56" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>449</v>
-      </c>
-      <c r="D57" t="s">
-        <v>450</v>
-      </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" t="s">
-        <v>346</v>
-      </c>
-      <c r="H57" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>451</v>
-      </c>
-      <c r="D58" t="s">
-        <v>452</v>
-      </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" t="s">
-        <v>35</v>
-      </c>
-      <c r="G58" t="s">
-        <v>346</v>
-      </c>
-      <c r="H58" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>453</v>
-      </c>
-      <c r="D59" t="s">
-        <v>454</v>
-      </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G59" t="s">
-        <v>346</v>
-      </c>
-      <c r="H59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>455</v>
-      </c>
-      <c r="D60" t="s">
-        <v>456</v>
-      </c>
-      <c r="E60" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" t="s">
-        <v>346</v>
-      </c>
-      <c r="H60" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>457</v>
-      </c>
-      <c r="D61" t="s">
-        <v>458</v>
-      </c>
-      <c r="E61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" t="s">
-        <v>346</v>
-      </c>
-      <c r="H61" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>459</v>
-      </c>
-      <c r="D62" t="s">
-        <v>460</v>
-      </c>
-      <c r="E62" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" t="s">
-        <v>346</v>
-      </c>
-      <c r="H62" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>461</v>
-      </c>
-      <c r="D63" t="s">
-        <v>462</v>
-      </c>
-      <c r="E63" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" t="s">
-        <v>346</v>
-      </c>
-      <c r="H63" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>463</v>
-      </c>
-      <c r="D64" t="s">
-        <v>464</v>
-      </c>
-      <c r="E64" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" t="s">
-        <v>35</v>
-      </c>
-      <c r="G64" t="s">
-        <v>346</v>
-      </c>
-      <c r="H64" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>465</v>
-      </c>
-      <c r="D65" t="s">
-        <v>466</v>
-      </c>
-      <c r="E65" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" t="s">
-        <v>35</v>
-      </c>
-      <c r="G65" t="s">
-        <v>346</v>
-      </c>
-      <c r="H65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" t="s">
-        <v>467</v>
-      </c>
-      <c r="D66" t="s">
-        <v>468</v>
-      </c>
-      <c r="E66" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" t="s">
-        <v>35</v>
-      </c>
-      <c r="G66" t="s">
-        <v>346</v>
-      </c>
-      <c r="H66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" t="s">
-        <v>469</v>
-      </c>
-      <c r="D67" t="s">
-        <v>470</v>
-      </c>
-      <c r="E67" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" t="s">
-        <v>35</v>
-      </c>
-      <c r="G67" t="s">
-        <v>346</v>
-      </c>
-      <c r="H67" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8">
-      <c r="B68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" t="s">
-        <v>471</v>
-      </c>
-      <c r="D68" t="s">
-        <v>472</v>
-      </c>
-      <c r="E68" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" t="s">
-        <v>35</v>
-      </c>
-      <c r="G68" t="s">
-        <v>346</v>
-      </c>
-      <c r="H68" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" t="s">
-        <v>473</v>
-      </c>
-      <c r="D69" t="s">
-        <v>474</v>
-      </c>
-      <c r="E69" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" t="s">
-        <v>35</v>
-      </c>
-      <c r="G69" t="s">
-        <v>346</v>
-      </c>
-      <c r="H69" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" t="s">
-        <v>475</v>
-      </c>
-      <c r="D70" t="s">
-        <v>476</v>
-      </c>
-      <c r="E70" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" t="s">
-        <v>35</v>
-      </c>
-      <c r="G70" t="s">
-        <v>346</v>
-      </c>
-      <c r="H70" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" t="s">
-        <v>477</v>
-      </c>
-      <c r="D71" t="s">
-        <v>478</v>
-      </c>
-      <c r="E71" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" t="s">
-        <v>346</v>
-      </c>
-      <c r="H71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" t="s">
-        <v>479</v>
-      </c>
-      <c r="D72" t="s">
-        <v>480</v>
-      </c>
-      <c r="E72" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" t="s">
-        <v>35</v>
-      </c>
-      <c r="G72" t="s">
-        <v>346</v>
-      </c>
-      <c r="H72" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" t="s">
-        <v>481</v>
-      </c>
-      <c r="D73" t="s">
-        <v>482</v>
-      </c>
-      <c r="E73" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" t="s">
-        <v>346</v>
-      </c>
-      <c r="H73" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="B74" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" t="s">
-        <v>483</v>
-      </c>
-      <c r="D74" t="s">
-        <v>484</v>
-      </c>
-      <c r="E74" t="s">
-        <v>25</v>
-      </c>
-      <c r="F74" t="s">
-        <v>35</v>
-      </c>
-      <c r="G74" t="s">
-        <v>346</v>
-      </c>
-      <c r="H74" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8">
-      <c r="B75" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" t="s">
-        <v>485</v>
-      </c>
-      <c r="D75" t="s">
-        <v>486</v>
-      </c>
-      <c r="E75" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" t="s">
-        <v>35</v>
-      </c>
-      <c r="G75" t="s">
-        <v>346</v>
-      </c>
-      <c r="H75" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" t="s">
-        <v>487</v>
-      </c>
-      <c r="D76" t="s">
-        <v>488</v>
-      </c>
-      <c r="E76" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" t="s">
-        <v>35</v>
-      </c>
-      <c r="G76" t="s">
-        <v>346</v>
-      </c>
-      <c r="H76" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="s">
-        <v>489</v>
-      </c>
-      <c r="D77" t="s">
-        <v>490</v>
-      </c>
-      <c r="E77" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77" t="s">
-        <v>35</v>
-      </c>
-      <c r="G77" t="s">
-        <v>346</v>
-      </c>
-      <c r="H77" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="B78" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" t="s">
-        <v>491</v>
-      </c>
-      <c r="D78" t="s">
-        <v>492</v>
-      </c>
-      <c r="E78" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78" t="s">
-        <v>35</v>
-      </c>
-      <c r="G78" t="s">
-        <v>346</v>
-      </c>
-      <c r="H78" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
-      <c r="B79" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" t="s">
-        <v>493</v>
-      </c>
-      <c r="D79" t="s">
-        <v>494</v>
-      </c>
-      <c r="E79" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" t="s">
-        <v>35</v>
-      </c>
-      <c r="G79" t="s">
-        <v>346</v>
-      </c>
-      <c r="H79" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8">
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>495</v>
-      </c>
-      <c r="D80" t="s">
-        <v>496</v>
-      </c>
-      <c r="E80" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" t="s">
-        <v>35</v>
-      </c>
-      <c r="G80" t="s">
-        <v>346</v>
-      </c>
-      <c r="H80" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
-      <c r="B81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>497</v>
-      </c>
-      <c r="D81" t="s">
-        <v>498</v>
-      </c>
-      <c r="E81" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" t="s">
-        <v>35</v>
-      </c>
-      <c r="G81" t="s">
-        <v>346</v>
-      </c>
-      <c r="H81" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" t="s">
-        <v>499</v>
-      </c>
-      <c r="D82" t="s">
-        <v>500</v>
-      </c>
-      <c r="E82" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" t="s">
-        <v>35</v>
-      </c>
-      <c r="G82" t="s">
-        <v>346</v>
-      </c>
-      <c r="H82" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>501</v>
-      </c>
-      <c r="D83" t="s">
-        <v>502</v>
-      </c>
-      <c r="E83" t="s">
-        <v>25</v>
-      </c>
-      <c r="F83" t="s">
-        <v>35</v>
-      </c>
-      <c r="G83" t="s">
-        <v>346</v>
-      </c>
-      <c r="H83" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8">
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="s">
-        <v>503</v>
-      </c>
-      <c r="D84" t="s">
-        <v>504</v>
-      </c>
-      <c r="E84" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" t="s">
-        <v>35</v>
-      </c>
-      <c r="G84" t="s">
-        <v>346</v>
-      </c>
-      <c r="H84" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" t="s">
-        <v>505</v>
-      </c>
-      <c r="D85" t="s">
-        <v>506</v>
-      </c>
-      <c r="E85" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G85" t="s">
-        <v>346</v>
-      </c>
-      <c r="H85" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8">
-      <c r="B86" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" t="s">
-        <v>507</v>
-      </c>
-      <c r="D86" t="s">
-        <v>508</v>
-      </c>
-      <c r="E86" t="s">
-        <v>25</v>
-      </c>
-      <c r="F86" t="s">
-        <v>35</v>
-      </c>
-      <c r="G86" t="s">
-        <v>346</v>
-      </c>
-      <c r="H86" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
-      <c r="B87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" t="s">
-        <v>509</v>
-      </c>
-      <c r="D87" t="s">
-        <v>510</v>
-      </c>
-      <c r="E87" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" t="s">
-        <v>35</v>
-      </c>
-      <c r="G87" t="s">
-        <v>346</v>
-      </c>
-      <c r="H87" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
-      <c r="B88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" t="s">
-        <v>511</v>
-      </c>
-      <c r="D88" t="s">
-        <v>512</v>
-      </c>
-      <c r="E88" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88" t="s">
-        <v>35</v>
-      </c>
-      <c r="G88" t="s">
-        <v>346</v>
-      </c>
-      <c r="H88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8">
-      <c r="B89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" t="s">
-        <v>513</v>
-      </c>
-      <c r="D89" t="s">
-        <v>514</v>
-      </c>
-      <c r="E89" t="s">
-        <v>25</v>
-      </c>
-      <c r="F89" t="s">
-        <v>35</v>
-      </c>
-      <c r="G89" t="s">
-        <v>346</v>
-      </c>
-      <c r="H89" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8">
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90" t="s">
-        <v>515</v>
-      </c>
-      <c r="D90" t="s">
-        <v>516</v>
-      </c>
-      <c r="E90" t="s">
-        <v>25</v>
-      </c>
-      <c r="F90" t="s">
-        <v>35</v>
-      </c>
-      <c r="G90" t="s">
-        <v>346</v>
-      </c>
-      <c r="H90" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8">
-      <c r="B91" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" t="s">
-        <v>517</v>
-      </c>
-      <c r="D91" t="s">
-        <v>518</v>
-      </c>
-      <c r="E91" t="s">
-        <v>25</v>
-      </c>
-      <c r="F91" t="s">
-        <v>35</v>
-      </c>
-      <c r="G91" t="s">
-        <v>346</v>
-      </c>
-      <c r="H91" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8">
-      <c r="B92" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>519</v>
-      </c>
-      <c r="D92" t="s">
-        <v>520</v>
-      </c>
-      <c r="E92" t="s">
-        <v>25</v>
-      </c>
-      <c r="F92" t="s">
-        <v>35</v>
-      </c>
-      <c r="G92" t="s">
-        <v>346</v>
-      </c>
-      <c r="H92" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8">
-      <c r="B93" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" t="s">
-        <v>521</v>
-      </c>
-      <c r="D93" t="s">
-        <v>522</v>
-      </c>
-      <c r="E93" t="s">
-        <v>25</v>
-      </c>
-      <c r="F93" t="s">
-        <v>35</v>
-      </c>
-      <c r="G93" t="s">
-        <v>346</v>
-      </c>
-      <c r="H93" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" t="s">
-        <v>523</v>
-      </c>
-      <c r="D94" t="s">
-        <v>524</v>
-      </c>
-      <c r="E94" t="s">
-        <v>25</v>
-      </c>
-      <c r="F94" t="s">
-        <v>35</v>
-      </c>
-      <c r="G94" t="s">
-        <v>346</v>
-      </c>
-      <c r="H94" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8">
-      <c r="B95" t="s">
-        <v>17</v>
-      </c>
-      <c r="C95" t="s">
-        <v>525</v>
-      </c>
-      <c r="D95" t="s">
-        <v>526</v>
-      </c>
-      <c r="E95" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" t="s">
-        <v>35</v>
-      </c>
-      <c r="G95" t="s">
-        <v>346</v>
-      </c>
-      <c r="H95" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8">
-      <c r="B96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C96" t="s">
-        <v>527</v>
-      </c>
-      <c r="D96" t="s">
-        <v>528</v>
-      </c>
-      <c r="E96" t="s">
-        <v>25</v>
-      </c>
-      <c r="F96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G96" t="s">
-        <v>346</v>
-      </c>
-      <c r="H96" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8">
-      <c r="B97" t="s">
-        <v>17</v>
-      </c>
-      <c r="C97" t="s">
-        <v>529</v>
-      </c>
-      <c r="D97" t="s">
-        <v>530</v>
-      </c>
-      <c r="E97" t="s">
-        <v>25</v>
-      </c>
-      <c r="F97" t="s">
-        <v>35</v>
-      </c>
-      <c r="G97" t="s">
-        <v>346</v>
-      </c>
-      <c r="H97" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="98" spans="2:8">
-      <c r="B98" t="s">
-        <v>17</v>
-      </c>
-      <c r="C98" t="s">
-        <v>531</v>
-      </c>
-      <c r="D98" t="s">
-        <v>532</v>
-      </c>
-      <c r="E98" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G98" t="s">
-        <v>346</v>
-      </c>
-      <c r="H98" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8">
-      <c r="B99" t="s">
-        <v>17</v>
-      </c>
-      <c r="C99" t="s">
-        <v>533</v>
-      </c>
-      <c r="D99" t="s">
-        <v>534</v>
-      </c>
-      <c r="E99" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" t="s">
-        <v>35</v>
-      </c>
-      <c r="G99" t="s">
-        <v>346</v>
-      </c>
-      <c r="H99" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8">
-      <c r="B100" t="s">
-        <v>17</v>
-      </c>
-      <c r="C100" t="s">
-        <v>535</v>
-      </c>
-      <c r="D100" t="s">
-        <v>536</v>
-      </c>
-      <c r="E100" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" t="s">
-        <v>35</v>
-      </c>
-      <c r="G100" t="s">
-        <v>346</v>
-      </c>
-      <c r="H100" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="101" spans="2:8">
-      <c r="B101" t="s">
-        <v>17</v>
-      </c>
-      <c r="C101" t="s">
-        <v>537</v>
-      </c>
-      <c r="D101" t="s">
-        <v>538</v>
-      </c>
-      <c r="E101" t="s">
-        <v>25</v>
-      </c>
-      <c r="F101" t="s">
-        <v>35</v>
-      </c>
-      <c r="G101" t="s">
-        <v>346</v>
-      </c>
-      <c r="H101" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="102" spans="2:8">
-      <c r="B102" t="s">
-        <v>17</v>
-      </c>
-      <c r="C102" t="s">
-        <v>539</v>
-      </c>
-      <c r="D102" t="s">
-        <v>540</v>
-      </c>
-      <c r="E102" t="s">
-        <v>25</v>
-      </c>
-      <c r="F102" t="s">
-        <v>35</v>
-      </c>
-      <c r="G102" t="s">
-        <v>346</v>
-      </c>
-      <c r="H102" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8">
-      <c r="B103" t="s">
-        <v>17</v>
-      </c>
-      <c r="C103" t="s">
-        <v>541</v>
-      </c>
-      <c r="D103" t="s">
-        <v>542</v>
-      </c>
-      <c r="E103" t="s">
-        <v>25</v>
-      </c>
-      <c r="F103" t="s">
-        <v>35</v>
-      </c>
-      <c r="G103" t="s">
-        <v>346</v>
-      </c>
-      <c r="H103" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8">
-      <c r="B104" t="s">
-        <v>17</v>
-      </c>
-      <c r="C104" t="s">
-        <v>543</v>
-      </c>
-      <c r="D104" t="s">
-        <v>544</v>
-      </c>
-      <c r="E104" t="s">
-        <v>25</v>
-      </c>
-      <c r="F104" t="s">
-        <v>35</v>
-      </c>
-      <c r="G104" t="s">
-        <v>346</v>
-      </c>
-      <c r="H104" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8">
-      <c r="B105" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" t="s">
-        <v>545</v>
-      </c>
-      <c r="D105" t="s">
-        <v>546</v>
-      </c>
-      <c r="E105" t="s">
-        <v>25</v>
-      </c>
-      <c r="F105" t="s">
-        <v>35</v>
-      </c>
-      <c r="G105" t="s">
-        <v>346</v>
-      </c>
-      <c r="H105" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8">
-      <c r="B106" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106" t="s">
-        <v>547</v>
-      </c>
-      <c r="D106" t="s">
-        <v>548</v>
-      </c>
-      <c r="E106" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" t="s">
-        <v>35</v>
-      </c>
-      <c r="G106" t="s">
-        <v>346</v>
-      </c>
-      <c r="H106" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8">
-      <c r="B107" t="s">
-        <v>17</v>
-      </c>
-      <c r="C107" t="s">
-        <v>549</v>
-      </c>
-      <c r="D107" t="s">
-        <v>550</v>
-      </c>
-      <c r="E107" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" t="s">
-        <v>35</v>
-      </c>
-      <c r="G107" t="s">
-        <v>346</v>
-      </c>
-      <c r="H107" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8">
-      <c r="B108" t="s">
-        <v>17</v>
-      </c>
-      <c r="C108" t="s">
-        <v>551</v>
-      </c>
-      <c r="D108" t="s">
-        <v>552</v>
-      </c>
-      <c r="E108" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" t="s">
-        <v>35</v>
-      </c>
-      <c r="G108" t="s">
-        <v>346</v>
-      </c>
-      <c r="H108" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8">
-      <c r="B109" t="s">
-        <v>17</v>
-      </c>
-      <c r="C109" t="s">
-        <v>553</v>
-      </c>
-      <c r="D109" t="s">
-        <v>554</v>
-      </c>
-      <c r="E109" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" t="s">
-        <v>35</v>
-      </c>
-      <c r="G109" t="s">
-        <v>346</v>
-      </c>
-      <c r="H109" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8">
-      <c r="B110" t="s">
-        <v>17</v>
-      </c>
-      <c r="C110" t="s">
-        <v>555</v>
-      </c>
-      <c r="D110" t="s">
-        <v>556</v>
-      </c>
-      <c r="E110" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" t="s">
-        <v>35</v>
-      </c>
-      <c r="G110" t="s">
-        <v>346</v>
-      </c>
-      <c r="H110" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8">
-      <c r="B111" t="s">
-        <v>17</v>
-      </c>
-      <c r="C111" t="s">
-        <v>557</v>
-      </c>
-      <c r="D111" t="s">
-        <v>558</v>
-      </c>
-      <c r="E111" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" t="s">
-        <v>35</v>
-      </c>
-      <c r="G111" t="s">
-        <v>346</v>
-      </c>
-      <c r="H111" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8">
-      <c r="B112" t="s">
-        <v>17</v>
-      </c>
-      <c r="C112" t="s">
-        <v>559</v>
-      </c>
-      <c r="D112" t="s">
-        <v>560</v>
-      </c>
-      <c r="E112" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" t="s">
-        <v>35</v>
-      </c>
-      <c r="G112" t="s">
-        <v>346</v>
-      </c>
-      <c r="H112" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8">
-      <c r="B113" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" t="s">
-        <v>561</v>
-      </c>
-      <c r="D113" t="s">
-        <v>562</v>
-      </c>
-      <c r="E113" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" t="s">
-        <v>35</v>
-      </c>
-      <c r="G113" t="s">
-        <v>346</v>
-      </c>
-      <c r="H113" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8">
-      <c r="B114" t="s">
-        <v>17</v>
-      </c>
-      <c r="C114" t="s">
-        <v>563</v>
-      </c>
-      <c r="D114" t="s">
-        <v>564</v>
-      </c>
-      <c r="E114" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" t="s">
-        <v>35</v>
-      </c>
-      <c r="G114" t="s">
-        <v>346</v>
-      </c>
-      <c r="H114" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8">
-      <c r="B115" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" t="s">
-        <v>565</v>
-      </c>
-      <c r="D115" t="s">
-        <v>566</v>
-      </c>
-      <c r="E115" t="s">
-        <v>25</v>
-      </c>
-      <c r="F115" t="s">
-        <v>35</v>
-      </c>
-      <c r="G115" t="s">
-        <v>346</v>
-      </c>
-      <c r="H115" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="116" spans="2:8">
-      <c r="B116" t="s">
-        <v>17</v>
-      </c>
-      <c r="C116" t="s">
-        <v>567</v>
-      </c>
-      <c r="D116" t="s">
-        <v>568</v>
-      </c>
-      <c r="E116" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" t="s">
-        <v>35</v>
-      </c>
-      <c r="G116" t="s">
-        <v>346</v>
-      </c>
-      <c r="H116" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="117" spans="2:8">
-      <c r="B117" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" t="s">
-        <v>569</v>
-      </c>
-      <c r="D117" t="s">
-        <v>570</v>
-      </c>
-      <c r="E117" t="s">
-        <v>25</v>
-      </c>
-      <c r="F117" t="s">
-        <v>35</v>
-      </c>
-      <c r="G117" t="s">
-        <v>346</v>
-      </c>
-      <c r="H117" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="118" spans="2:8">
-      <c r="B118" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" t="s">
-        <v>571</v>
-      </c>
-      <c r="D118" t="s">
-        <v>572</v>
-      </c>
-      <c r="E118" t="s">
-        <v>25</v>
-      </c>
-      <c r="F118" t="s">
-        <v>35</v>
-      </c>
-      <c r="G118" t="s">
-        <v>346</v>
-      </c>
-      <c r="H118" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8">
-      <c r="B119" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" t="s">
-        <v>573</v>
-      </c>
-      <c r="D119" t="s">
-        <v>574</v>
-      </c>
-      <c r="E119" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" t="s">
-        <v>35</v>
-      </c>
-      <c r="G119" t="s">
-        <v>346</v>
-      </c>
-      <c r="H119" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8">
-      <c r="B120" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" t="s">
-        <v>575</v>
-      </c>
-      <c r="D120" t="s">
-        <v>576</v>
-      </c>
-      <c r="E120" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" t="s">
-        <v>35</v>
-      </c>
-      <c r="G120" t="s">
-        <v>346</v>
-      </c>
-      <c r="H120" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8">
-      <c r="B121" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" t="s">
-        <v>577</v>
-      </c>
-      <c r="D121" t="s">
-        <v>578</v>
-      </c>
-      <c r="E121" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" t="s">
-        <v>35</v>
-      </c>
-      <c r="G121" t="s">
-        <v>346</v>
-      </c>
-      <c r="H121" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8">
-      <c r="B122" t="s">
-        <v>17</v>
-      </c>
-      <c r="C122" t="s">
-        <v>579</v>
-      </c>
-      <c r="D122" t="s">
-        <v>580</v>
-      </c>
-      <c r="E122" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" t="s">
-        <v>35</v>
-      </c>
-      <c r="G122" t="s">
-        <v>346</v>
-      </c>
-      <c r="H122" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="123" spans="2:8">
-      <c r="B123" t="s">
-        <v>17</v>
-      </c>
-      <c r="C123" t="s">
-        <v>581</v>
-      </c>
-      <c r="D123" t="s">
-        <v>582</v>
-      </c>
-      <c r="E123" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" t="s">
-        <v>35</v>
-      </c>
-      <c r="G123" t="s">
-        <v>346</v>
-      </c>
-      <c r="H123" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8">
-      <c r="B124" t="s">
-        <v>17</v>
-      </c>
-      <c r="C124" t="s">
-        <v>583</v>
-      </c>
-      <c r="D124" t="s">
-        <v>584</v>
-      </c>
-      <c r="E124" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" t="s">
-        <v>35</v>
-      </c>
-      <c r="G124" t="s">
-        <v>346</v>
-      </c>
-      <c r="H124" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="125" spans="2:8">
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" t="s">
-        <v>585</v>
-      </c>
-      <c r="D125" t="s">
-        <v>586</v>
-      </c>
-      <c r="E125" t="s">
-        <v>25</v>
-      </c>
-      <c r="F125" t="s">
-        <v>35</v>
-      </c>
-      <c r="G125" t="s">
-        <v>346</v>
-      </c>
-      <c r="H125" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8">
-      <c r="B126" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" t="s">
-        <v>587</v>
-      </c>
-      <c r="D126" t="s">
-        <v>588</v>
-      </c>
-      <c r="E126" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" t="s">
-        <v>35</v>
-      </c>
-      <c r="G126" t="s">
-        <v>346</v>
-      </c>
-      <c r="H126" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="127" spans="2:8">
-      <c r="B127" t="s">
-        <v>17</v>
-      </c>
-      <c r="C127" t="s">
-        <v>589</v>
-      </c>
-      <c r="D127" t="s">
-        <v>590</v>
-      </c>
-      <c r="E127" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" t="s">
-        <v>35</v>
-      </c>
-      <c r="G127" t="s">
-        <v>346</v>
-      </c>
-      <c r="H127" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="128" spans="2:8">
-      <c r="B128" t="s">
-        <v>17</v>
-      </c>
-      <c r="C128" t="s">
-        <v>591</v>
-      </c>
-      <c r="D128" t="s">
-        <v>592</v>
-      </c>
-      <c r="E128" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" t="s">
-        <v>35</v>
-      </c>
-      <c r="G128" t="s">
-        <v>346</v>
-      </c>
-      <c r="H128" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8">
-      <c r="B129" t="s">
-        <v>17</v>
-      </c>
-      <c r="C129" t="s">
-        <v>593</v>
-      </c>
-      <c r="D129" t="s">
-        <v>594</v>
-      </c>
-      <c r="E129" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" t="s">
-        <v>35</v>
-      </c>
-      <c r="G129" t="s">
-        <v>346</v>
-      </c>
-      <c r="H129" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="130" spans="2:8">
-      <c r="B130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C130" t="s">
-        <v>595</v>
-      </c>
-      <c r="D130" t="s">
-        <v>596</v>
-      </c>
-      <c r="E130" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" t="s">
-        <v>35</v>
-      </c>
-      <c r="G130" t="s">
-        <v>346</v>
-      </c>
-      <c r="H130" t="s">
-        <v>216</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R68"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -7239,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -7271,10 +4338,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -7283,7 +4350,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -7300,10 +4367,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -7312,7 +4379,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -7329,10 +4396,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -7341,7 +4408,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -7358,10 +4425,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -7370,7 +4437,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -7387,10 +4454,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -7399,7 +4466,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -7416,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -7428,7 +4495,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -7445,10 +4512,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -7457,7 +4524,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -7474,10 +4541,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -7486,7 +4553,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -7503,10 +4570,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -7515,7 +4582,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -7535,10 +4602,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -7547,7 +4614,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -7567,10 +4634,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -7579,7 +4646,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -7608,10 +4675,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -7620,7 +4687,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -7640,10 +4707,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -7652,7 +4719,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -7672,10 +4739,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -7684,7 +4751,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -7704,10 +4771,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -7716,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -7736,10 +4803,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -7748,7 +4815,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -7774,10 +4841,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -7786,7 +4853,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -7806,10 +4873,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -7818,7 +4885,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -7835,10 +4902,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -7847,7 +4914,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -7864,10 +4931,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -7876,7 +4943,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -7884,10 +4951,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -7896,7 +4963,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -7904,10 +4971,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -7916,7 +4983,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -7924,10 +4991,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -7936,7 +5003,7 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -7944,10 +5011,10 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -7956,7 +5023,7 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -7964,10 +5031,10 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -7976,7 +5043,7 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -7984,10 +5051,10 @@
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -7996,7 +5063,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -8004,10 +5071,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -8016,7 +5083,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -8024,10 +5091,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -8036,7 +5103,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -8044,10 +5111,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -8056,7 +5123,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -8064,10 +5131,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -8076,7 +5143,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -8084,10 +5151,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -8096,7 +5163,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -8104,10 +5171,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -8116,7 +5183,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -8124,10 +5191,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -8136,7 +5203,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -8144,10 +5211,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -8156,7 +5223,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -8164,10 +5231,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -8176,7 +5243,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -8184,10 +5251,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -8196,7 +5263,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -8204,10 +5271,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O41" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -8216,7 +5283,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -8224,10 +5291,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -8236,7 +5303,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -8244,10 +5311,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -8256,7 +5323,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -8264,10 +5331,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -8276,7 +5343,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -8284,10 +5351,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -8296,7 +5363,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -8304,10 +5371,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O46" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -8316,7 +5383,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -8324,10 +5391,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -8336,7 +5403,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -8344,10 +5411,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -8356,7 +5423,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -8364,10 +5431,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -8376,7 +5443,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -8384,10 +5451,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -8396,7 +5463,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -8404,10 +5471,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -8416,7 +5483,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -8424,10 +5491,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -8436,7 +5503,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -8444,10 +5511,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -8456,7 +5523,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -8464,10 +5531,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -8476,7 +5543,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -8484,10 +5551,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -8496,7 +5563,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -8504,10 +5571,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -8516,7 +5583,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -8524,10 +5591,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -8536,7 +5603,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -8544,10 +5611,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -8556,7 +5623,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -8564,10 +5631,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O59" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -8576,7 +5643,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -8584,10 +5651,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O60" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -8596,7 +5663,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -8604,10 +5671,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -8616,7 +5683,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -8624,10 +5691,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -8636,7 +5703,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -8644,10 +5711,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -8656,7 +5723,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -8664,10 +5731,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -8676,7 +5743,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -8684,10 +5751,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O65" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -8696,7 +5763,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -8704,10 +5771,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O66" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -8716,7 +5783,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -8724,10 +5791,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -8736,7 +5803,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -8744,10 +5811,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -8756,7 +5823,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -8767,7 +5834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
@@ -9045,9 +6112,2945 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA1FF0B-AA8E-42A9-91AC-027707DD955B}">
+  <dimension ref="B3:H130"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>347</v>
+      </c>
+      <c r="H7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>347</v>
+      </c>
+      <c r="H8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>347</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>356</v>
+      </c>
+      <c r="D10" t="s">
+        <v>357</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>347</v>
+      </c>
+      <c r="H10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D11" t="s">
+        <v>359</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>347</v>
+      </c>
+      <c r="H11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>347</v>
+      </c>
+      <c r="H12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>347</v>
+      </c>
+      <c r="H13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" t="s">
+        <v>365</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>347</v>
+      </c>
+      <c r="H14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>347</v>
+      </c>
+      <c r="H15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" t="s">
+        <v>369</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>347</v>
+      </c>
+      <c r="H16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D17" t="s">
+        <v>371</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>347</v>
+      </c>
+      <c r="H17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" t="s">
+        <v>373</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>347</v>
+      </c>
+      <c r="H18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" t="s">
+        <v>375</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>347</v>
+      </c>
+      <c r="H19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>376</v>
+      </c>
+      <c r="D20" t="s">
+        <v>377</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>347</v>
+      </c>
+      <c r="H20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D21" t="s">
+        <v>379</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>347</v>
+      </c>
+      <c r="H21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>380</v>
+      </c>
+      <c r="D22" t="s">
+        <v>381</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>347</v>
+      </c>
+      <c r="H22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>382</v>
+      </c>
+      <c r="D23" t="s">
+        <v>383</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>347</v>
+      </c>
+      <c r="H23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>384</v>
+      </c>
+      <c r="D24" t="s">
+        <v>385</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>347</v>
+      </c>
+      <c r="H24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>386</v>
+      </c>
+      <c r="D25" t="s">
+        <v>387</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>347</v>
+      </c>
+      <c r="H25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>388</v>
+      </c>
+      <c r="D26" t="s">
+        <v>389</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>347</v>
+      </c>
+      <c r="H26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D27" t="s">
+        <v>391</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s">
+        <v>347</v>
+      </c>
+      <c r="H27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>392</v>
+      </c>
+      <c r="D28" t="s">
+        <v>393</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>347</v>
+      </c>
+      <c r="H28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" t="s">
+        <v>395</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s">
+        <v>347</v>
+      </c>
+      <c r="H29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>396</v>
+      </c>
+      <c r="D30" t="s">
+        <v>397</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" t="s">
+        <v>347</v>
+      </c>
+      <c r="H30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>398</v>
+      </c>
+      <c r="D31" t="s">
+        <v>399</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>347</v>
+      </c>
+      <c r="H31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" t="s">
+        <v>401</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>347</v>
+      </c>
+      <c r="H32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" t="s">
+        <v>403</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G33" t="s">
+        <v>347</v>
+      </c>
+      <c r="H33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>404</v>
+      </c>
+      <c r="D34" t="s">
+        <v>405</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>347</v>
+      </c>
+      <c r="H34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>406</v>
+      </c>
+      <c r="D35" t="s">
+        <v>407</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>347</v>
+      </c>
+      <c r="H35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>408</v>
+      </c>
+      <c r="D36" t="s">
+        <v>409</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" t="s">
+        <v>347</v>
+      </c>
+      <c r="H36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>410</v>
+      </c>
+      <c r="D37" t="s">
+        <v>411</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>347</v>
+      </c>
+      <c r="H37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" t="s">
+        <v>412</v>
+      </c>
+      <c r="D38" t="s">
+        <v>413</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>347</v>
+      </c>
+      <c r="H38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>414</v>
+      </c>
+      <c r="D39" t="s">
+        <v>415</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" t="s">
+        <v>347</v>
+      </c>
+      <c r="H39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>416</v>
+      </c>
+      <c r="D40" t="s">
+        <v>417</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>347</v>
+      </c>
+      <c r="H40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>418</v>
+      </c>
+      <c r="D41" t="s">
+        <v>419</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" t="s">
+        <v>347</v>
+      </c>
+      <c r="H41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>420</v>
+      </c>
+      <c r="D42" t="s">
+        <v>421</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" t="s">
+        <v>347</v>
+      </c>
+      <c r="H42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>422</v>
+      </c>
+      <c r="D43" t="s">
+        <v>423</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" t="s">
+        <v>347</v>
+      </c>
+      <c r="H43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>424</v>
+      </c>
+      <c r="D44" t="s">
+        <v>425</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" t="s">
+        <v>347</v>
+      </c>
+      <c r="H44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D45" t="s">
+        <v>427</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>347</v>
+      </c>
+      <c r="H45" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>428</v>
+      </c>
+      <c r="D46" t="s">
+        <v>429</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
+        <v>347</v>
+      </c>
+      <c r="H46" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>430</v>
+      </c>
+      <c r="D47" t="s">
+        <v>431</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+      <c r="D48" t="s">
+        <v>433</v>
+      </c>
+      <c r="E48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>347</v>
+      </c>
+      <c r="H48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>434</v>
+      </c>
+      <c r="D49" t="s">
+        <v>435</v>
+      </c>
+      <c r="E49" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>347</v>
+      </c>
+      <c r="H49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
+        <v>437</v>
+      </c>
+      <c r="E50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>347</v>
+      </c>
+      <c r="H50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" t="s">
+        <v>439</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" t="s">
+        <v>347</v>
+      </c>
+      <c r="H51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>440</v>
+      </c>
+      <c r="D52" t="s">
+        <v>441</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" t="s">
+        <v>347</v>
+      </c>
+      <c r="H52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>442</v>
+      </c>
+      <c r="D53" t="s">
+        <v>443</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" t="s">
+        <v>347</v>
+      </c>
+      <c r="H53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>444</v>
+      </c>
+      <c r="D54" t="s">
+        <v>445</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" t="s">
+        <v>347</v>
+      </c>
+      <c r="H54" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>446</v>
+      </c>
+      <c r="D55" t="s">
+        <v>447</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55" t="s">
+        <v>347</v>
+      </c>
+      <c r="H55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>448</v>
+      </c>
+      <c r="D56" t="s">
+        <v>449</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" t="s">
+        <v>347</v>
+      </c>
+      <c r="H56" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>450</v>
+      </c>
+      <c r="D57" t="s">
+        <v>451</v>
+      </c>
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" t="s">
+        <v>347</v>
+      </c>
+      <c r="H57" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>452</v>
+      </c>
+      <c r="D58" t="s">
+        <v>453</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s">
+        <v>347</v>
+      </c>
+      <c r="H58" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>454</v>
+      </c>
+      <c r="D59" t="s">
+        <v>455</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
+        <v>347</v>
+      </c>
+      <c r="H59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>456</v>
+      </c>
+      <c r="D60" t="s">
+        <v>457</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s">
+        <v>347</v>
+      </c>
+      <c r="H60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>458</v>
+      </c>
+      <c r="D61" t="s">
+        <v>459</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s">
+        <v>347</v>
+      </c>
+      <c r="H61" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>460</v>
+      </c>
+      <c r="D62" t="s">
+        <v>461</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" t="s">
+        <v>347</v>
+      </c>
+      <c r="H62" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>462</v>
+      </c>
+      <c r="D63" t="s">
+        <v>463</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" t="s">
+        <v>347</v>
+      </c>
+      <c r="H63" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>464</v>
+      </c>
+      <c r="D64" t="s">
+        <v>465</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>347</v>
+      </c>
+      <c r="H64" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" t="s">
+        <v>466</v>
+      </c>
+      <c r="D65" t="s">
+        <v>467</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" t="s">
+        <v>347</v>
+      </c>
+      <c r="H65" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>468</v>
+      </c>
+      <c r="D66" t="s">
+        <v>469</v>
+      </c>
+      <c r="E66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
+        <v>347</v>
+      </c>
+      <c r="H66" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" t="s">
+        <v>470</v>
+      </c>
+      <c r="D67" t="s">
+        <v>471</v>
+      </c>
+      <c r="E67" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" t="s">
+        <v>347</v>
+      </c>
+      <c r="H67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="B68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" t="s">
+        <v>472</v>
+      </c>
+      <c r="D68" t="s">
+        <v>473</v>
+      </c>
+      <c r="E68" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" t="s">
+        <v>347</v>
+      </c>
+      <c r="H68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" t="s">
+        <v>474</v>
+      </c>
+      <c r="D69" t="s">
+        <v>475</v>
+      </c>
+      <c r="E69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" t="s">
+        <v>347</v>
+      </c>
+      <c r="H69" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8">
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" t="s">
+        <v>476</v>
+      </c>
+      <c r="D70" t="s">
+        <v>477</v>
+      </c>
+      <c r="E70" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" t="s">
+        <v>35</v>
+      </c>
+      <c r="G70" t="s">
+        <v>347</v>
+      </c>
+      <c r="H70" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8">
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" t="s">
+        <v>478</v>
+      </c>
+      <c r="D71" t="s">
+        <v>479</v>
+      </c>
+      <c r="E71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" t="s">
+        <v>347</v>
+      </c>
+      <c r="H71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8">
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>480</v>
+      </c>
+      <c r="D72" t="s">
+        <v>481</v>
+      </c>
+      <c r="E72" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" t="s">
+        <v>347</v>
+      </c>
+      <c r="H72" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" t="s">
+        <v>482</v>
+      </c>
+      <c r="D73" t="s">
+        <v>483</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" t="s">
+        <v>347</v>
+      </c>
+      <c r="H73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>484</v>
+      </c>
+      <c r="D74" t="s">
+        <v>485</v>
+      </c>
+      <c r="E74" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" t="s">
+        <v>347</v>
+      </c>
+      <c r="H74" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8">
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>486</v>
+      </c>
+      <c r="D75" t="s">
+        <v>487</v>
+      </c>
+      <c r="E75" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" t="s">
+        <v>35</v>
+      </c>
+      <c r="G75" t="s">
+        <v>347</v>
+      </c>
+      <c r="H75" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>488</v>
+      </c>
+      <c r="D76" t="s">
+        <v>489</v>
+      </c>
+      <c r="E76" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" t="s">
+        <v>347</v>
+      </c>
+      <c r="H76" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>490</v>
+      </c>
+      <c r="D77" t="s">
+        <v>491</v>
+      </c>
+      <c r="E77" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" t="s">
+        <v>35</v>
+      </c>
+      <c r="G77" t="s">
+        <v>347</v>
+      </c>
+      <c r="H77" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>492</v>
+      </c>
+      <c r="D78" t="s">
+        <v>493</v>
+      </c>
+      <c r="E78" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" t="s">
+        <v>347</v>
+      </c>
+      <c r="H78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>494</v>
+      </c>
+      <c r="D79" t="s">
+        <v>495</v>
+      </c>
+      <c r="E79" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" t="s">
+        <v>347</v>
+      </c>
+      <c r="H79" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>496</v>
+      </c>
+      <c r="D80" t="s">
+        <v>497</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" t="s">
+        <v>347</v>
+      </c>
+      <c r="H80" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>498</v>
+      </c>
+      <c r="D81" t="s">
+        <v>499</v>
+      </c>
+      <c r="E81" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" t="s">
+        <v>35</v>
+      </c>
+      <c r="G81" t="s">
+        <v>347</v>
+      </c>
+      <c r="H81" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>500</v>
+      </c>
+      <c r="D82" t="s">
+        <v>501</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" t="s">
+        <v>35</v>
+      </c>
+      <c r="G82" t="s">
+        <v>347</v>
+      </c>
+      <c r="H82" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8">
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>502</v>
+      </c>
+      <c r="D83" t="s">
+        <v>503</v>
+      </c>
+      <c r="E83" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" t="s">
+        <v>35</v>
+      </c>
+      <c r="G83" t="s">
+        <v>347</v>
+      </c>
+      <c r="H83" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>504</v>
+      </c>
+      <c r="D84" t="s">
+        <v>505</v>
+      </c>
+      <c r="E84" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" t="s">
+        <v>35</v>
+      </c>
+      <c r="G84" t="s">
+        <v>347</v>
+      </c>
+      <c r="H84" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8">
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>506</v>
+      </c>
+      <c r="D85" t="s">
+        <v>507</v>
+      </c>
+      <c r="E85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" t="s">
+        <v>35</v>
+      </c>
+      <c r="G85" t="s">
+        <v>347</v>
+      </c>
+      <c r="H85" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>508</v>
+      </c>
+      <c r="D86" t="s">
+        <v>509</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>35</v>
+      </c>
+      <c r="G86" t="s">
+        <v>347</v>
+      </c>
+      <c r="H86" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8">
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>510</v>
+      </c>
+      <c r="D87" t="s">
+        <v>511</v>
+      </c>
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" t="s">
+        <v>347</v>
+      </c>
+      <c r="H87" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>512</v>
+      </c>
+      <c r="D88" t="s">
+        <v>513</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" t="s">
+        <v>347</v>
+      </c>
+      <c r="H88" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8">
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>514</v>
+      </c>
+      <c r="D89" t="s">
+        <v>515</v>
+      </c>
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" t="s">
+        <v>35</v>
+      </c>
+      <c r="G89" t="s">
+        <v>347</v>
+      </c>
+      <c r="H89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>516</v>
+      </c>
+      <c r="D90" t="s">
+        <v>517</v>
+      </c>
+      <c r="E90" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" t="s">
+        <v>35</v>
+      </c>
+      <c r="G90" t="s">
+        <v>347</v>
+      </c>
+      <c r="H90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>518</v>
+      </c>
+      <c r="D91" t="s">
+        <v>519</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>35</v>
+      </c>
+      <c r="G91" t="s">
+        <v>347</v>
+      </c>
+      <c r="H91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8">
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>520</v>
+      </c>
+      <c r="D92" t="s">
+        <v>521</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" t="s">
+        <v>35</v>
+      </c>
+      <c r="G92" t="s">
+        <v>347</v>
+      </c>
+      <c r="H92" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8">
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>522</v>
+      </c>
+      <c r="D93" t="s">
+        <v>523</v>
+      </c>
+      <c r="E93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" t="s">
+        <v>35</v>
+      </c>
+      <c r="G93" t="s">
+        <v>347</v>
+      </c>
+      <c r="H93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>524</v>
+      </c>
+      <c r="D94" t="s">
+        <v>525</v>
+      </c>
+      <c r="E94" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" t="s">
+        <v>35</v>
+      </c>
+      <c r="G94" t="s">
+        <v>347</v>
+      </c>
+      <c r="H94" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8">
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>526</v>
+      </c>
+      <c r="D95" t="s">
+        <v>527</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>35</v>
+      </c>
+      <c r="G95" t="s">
+        <v>347</v>
+      </c>
+      <c r="H95" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>528</v>
+      </c>
+      <c r="D96" t="s">
+        <v>529</v>
+      </c>
+      <c r="E96" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G96" t="s">
+        <v>347</v>
+      </c>
+      <c r="H96" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8">
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>530</v>
+      </c>
+      <c r="D97" t="s">
+        <v>531</v>
+      </c>
+      <c r="E97" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" t="s">
+        <v>35</v>
+      </c>
+      <c r="G97" t="s">
+        <v>347</v>
+      </c>
+      <c r="H97" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8">
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>532</v>
+      </c>
+      <c r="D98" t="s">
+        <v>533</v>
+      </c>
+      <c r="E98" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" t="s">
+        <v>347</v>
+      </c>
+      <c r="H98" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8">
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>534</v>
+      </c>
+      <c r="D99" t="s">
+        <v>535</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>35</v>
+      </c>
+      <c r="G99" t="s">
+        <v>347</v>
+      </c>
+      <c r="H99" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>536</v>
+      </c>
+      <c r="D100" t="s">
+        <v>537</v>
+      </c>
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>35</v>
+      </c>
+      <c r="G100" t="s">
+        <v>347</v>
+      </c>
+      <c r="H100" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8">
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>538</v>
+      </c>
+      <c r="D101" t="s">
+        <v>539</v>
+      </c>
+      <c r="E101" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" t="s">
+        <v>35</v>
+      </c>
+      <c r="G101" t="s">
+        <v>347</v>
+      </c>
+      <c r="H101" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>540</v>
+      </c>
+      <c r="D102" t="s">
+        <v>541</v>
+      </c>
+      <c r="E102" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" t="s">
+        <v>35</v>
+      </c>
+      <c r="G102" t="s">
+        <v>347</v>
+      </c>
+      <c r="H102" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>542</v>
+      </c>
+      <c r="D103" t="s">
+        <v>543</v>
+      </c>
+      <c r="E103" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" t="s">
+        <v>35</v>
+      </c>
+      <c r="G103" t="s">
+        <v>347</v>
+      </c>
+      <c r="H103" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>544</v>
+      </c>
+      <c r="D104" t="s">
+        <v>545</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>35</v>
+      </c>
+      <c r="G104" t="s">
+        <v>347</v>
+      </c>
+      <c r="H104" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8">
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>546</v>
+      </c>
+      <c r="D105" t="s">
+        <v>547</v>
+      </c>
+      <c r="E105" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" t="s">
+        <v>35</v>
+      </c>
+      <c r="G105" t="s">
+        <v>347</v>
+      </c>
+      <c r="H105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>548</v>
+      </c>
+      <c r="D106" t="s">
+        <v>549</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>35</v>
+      </c>
+      <c r="G106" t="s">
+        <v>347</v>
+      </c>
+      <c r="H106" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8">
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>550</v>
+      </c>
+      <c r="D107" t="s">
+        <v>551</v>
+      </c>
+      <c r="E107" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" t="s">
+        <v>347</v>
+      </c>
+      <c r="H107" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8">
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>552</v>
+      </c>
+      <c r="D108" t="s">
+        <v>553</v>
+      </c>
+      <c r="E108" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" t="s">
+        <v>347</v>
+      </c>
+      <c r="H108" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8">
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>554</v>
+      </c>
+      <c r="D109" t="s">
+        <v>555</v>
+      </c>
+      <c r="E109" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" t="s">
+        <v>35</v>
+      </c>
+      <c r="G109" t="s">
+        <v>347</v>
+      </c>
+      <c r="H109" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8">
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>556</v>
+      </c>
+      <c r="D110" t="s">
+        <v>557</v>
+      </c>
+      <c r="E110" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" t="s">
+        <v>347</v>
+      </c>
+      <c r="H110" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8">
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>558</v>
+      </c>
+      <c r="D111" t="s">
+        <v>559</v>
+      </c>
+      <c r="E111" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" t="s">
+        <v>35</v>
+      </c>
+      <c r="G111" t="s">
+        <v>347</v>
+      </c>
+      <c r="H111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8">
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>560</v>
+      </c>
+      <c r="D112" t="s">
+        <v>561</v>
+      </c>
+      <c r="E112" t="s">
+        <v>25</v>
+      </c>
+      <c r="F112" t="s">
+        <v>35</v>
+      </c>
+      <c r="G112" t="s">
+        <v>347</v>
+      </c>
+      <c r="H112" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8">
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>562</v>
+      </c>
+      <c r="D113" t="s">
+        <v>563</v>
+      </c>
+      <c r="E113" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" t="s">
+        <v>35</v>
+      </c>
+      <c r="G113" t="s">
+        <v>347</v>
+      </c>
+      <c r="H113" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8">
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>564</v>
+      </c>
+      <c r="D114" t="s">
+        <v>565</v>
+      </c>
+      <c r="E114" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" t="s">
+        <v>35</v>
+      </c>
+      <c r="G114" t="s">
+        <v>347</v>
+      </c>
+      <c r="H114" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8">
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>566</v>
+      </c>
+      <c r="D115" t="s">
+        <v>567</v>
+      </c>
+      <c r="E115" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115" t="s">
+        <v>35</v>
+      </c>
+      <c r="G115" t="s">
+        <v>347</v>
+      </c>
+      <c r="H115" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8">
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>568</v>
+      </c>
+      <c r="D116" t="s">
+        <v>569</v>
+      </c>
+      <c r="E116" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116" t="s">
+        <v>35</v>
+      </c>
+      <c r="G116" t="s">
+        <v>347</v>
+      </c>
+      <c r="H116" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8">
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" t="s">
+        <v>570</v>
+      </c>
+      <c r="D117" t="s">
+        <v>571</v>
+      </c>
+      <c r="E117" t="s">
+        <v>25</v>
+      </c>
+      <c r="F117" t="s">
+        <v>35</v>
+      </c>
+      <c r="G117" t="s">
+        <v>347</v>
+      </c>
+      <c r="H117" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8">
+      <c r="B118" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" t="s">
+        <v>572</v>
+      </c>
+      <c r="D118" t="s">
+        <v>573</v>
+      </c>
+      <c r="E118" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118" t="s">
+        <v>35</v>
+      </c>
+      <c r="G118" t="s">
+        <v>347</v>
+      </c>
+      <c r="H118" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8">
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" t="s">
+        <v>574</v>
+      </c>
+      <c r="D119" t="s">
+        <v>575</v>
+      </c>
+      <c r="E119" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" t="s">
+        <v>347</v>
+      </c>
+      <c r="H119" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8">
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" t="s">
+        <v>576</v>
+      </c>
+      <c r="D120" t="s">
+        <v>577</v>
+      </c>
+      <c r="E120" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" t="s">
+        <v>347</v>
+      </c>
+      <c r="H120" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8">
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>578</v>
+      </c>
+      <c r="D121" t="s">
+        <v>579</v>
+      </c>
+      <c r="E121" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" t="s">
+        <v>35</v>
+      </c>
+      <c r="G121" t="s">
+        <v>347</v>
+      </c>
+      <c r="H121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8">
+      <c r="B122" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122" t="s">
+        <v>580</v>
+      </c>
+      <c r="D122" t="s">
+        <v>581</v>
+      </c>
+      <c r="E122" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" t="s">
+        <v>35</v>
+      </c>
+      <c r="G122" t="s">
+        <v>347</v>
+      </c>
+      <c r="H122" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8">
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>582</v>
+      </c>
+      <c r="D123" t="s">
+        <v>583</v>
+      </c>
+      <c r="E123" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" t="s">
+        <v>35</v>
+      </c>
+      <c r="G123" t="s">
+        <v>347</v>
+      </c>
+      <c r="H123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8">
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" t="s">
+        <v>584</v>
+      </c>
+      <c r="D124" t="s">
+        <v>585</v>
+      </c>
+      <c r="E124" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124" t="s">
+        <v>35</v>
+      </c>
+      <c r="G124" t="s">
+        <v>347</v>
+      </c>
+      <c r="H124" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8">
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
+        <v>586</v>
+      </c>
+      <c r="D125" t="s">
+        <v>587</v>
+      </c>
+      <c r="E125" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" t="s">
+        <v>35</v>
+      </c>
+      <c r="G125" t="s">
+        <v>347</v>
+      </c>
+      <c r="H125" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8">
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" t="s">
+        <v>588</v>
+      </c>
+      <c r="D126" t="s">
+        <v>589</v>
+      </c>
+      <c r="E126" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" t="s">
+        <v>35</v>
+      </c>
+      <c r="G126" t="s">
+        <v>347</v>
+      </c>
+      <c r="H126" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8">
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" t="s">
+        <v>590</v>
+      </c>
+      <c r="D127" t="s">
+        <v>591</v>
+      </c>
+      <c r="E127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" t="s">
+        <v>35</v>
+      </c>
+      <c r="G127" t="s">
+        <v>347</v>
+      </c>
+      <c r="H127" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8">
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>592</v>
+      </c>
+      <c r="D128" t="s">
+        <v>593</v>
+      </c>
+      <c r="E128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" t="s">
+        <v>35</v>
+      </c>
+      <c r="G128" t="s">
+        <v>347</v>
+      </c>
+      <c r="H128" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8">
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>594</v>
+      </c>
+      <c r="D129" t="s">
+        <v>595</v>
+      </c>
+      <c r="E129" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" t="s">
+        <v>35</v>
+      </c>
+      <c r="G129" t="s">
+        <v>347</v>
+      </c>
+      <c r="H129" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8">
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>596</v>
+      </c>
+      <c r="D130" t="s">
+        <v>597</v>
+      </c>
+      <c r="E130" t="s">
+        <v>25</v>
+      </c>
+      <c r="F130" t="s">
+        <v>35</v>
+      </c>
+      <c r="G130" t="s">
+        <v>347</v>
+      </c>
+      <c r="H130" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -9189,49 +9192,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -9239,22 +9242,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -9278,20 +9281,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -9607,6 +9606,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
